--- a/technology_surveys/032_data_analytics_utilization_survey--technology_surveys.xlsx
+++ b/technology_surveys/032_data_analytics_utilization_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'tableau',_'value':_'tableau'}</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Tableau', 'value': 'Tableau'}</t>
+          <t>Tableau</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'power_bi',_'value':_'power_bi'}</t>
+          <t>power_bi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Power BI', 'value': 'Power BI'}</t>
+          <t>Power BI</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'qlik',_'value':_'qlik'}</t>
+          <t>qlik</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Qlik', 'value': 'Qlik'}</t>
+          <t>Qlik</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'google_bigquery',_'value':_'google_bigquery'}</t>
+          <t>google_bigquery</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Google BigQuery', 'value': 'Google BigQuery'}</t>
+          <t>Google BigQuery</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'amazon_redshift',_'value':_'amazon_redshift'}</t>
+          <t>amazon_redshift</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Amazon Redshift', 'value': 'Amazon Redshift'}</t>
+          <t>Amazon Redshift</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'google',_'value':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Google', 'value': 'Google'}</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jotform',_'value':_'jotform'}</t>
+          <t>jotform</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jotform', 'value': 'Jotform'}</t>
+          <t>Jotform</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'google',_'value':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Google', 'value': 'Google'}</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jotform',_'value':_'jotform'}</t>
+          <t>jotform</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jotform', 'value': 'Jotform'}</t>
+          <t>Jotform</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'technology_surveys',_'value':_'technology_surveys'}</t>
+          <t>technology_surveys</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Technology Surveys', 'value': 'Technology Surveys'}</t>
+          <t>Technology Surveys</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
